--- a/Sets-DemoModels.xlsx
+++ b/Sets-DemoModels.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda2\Veda_models\Basic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aghedupl.sharepoint.com/sites/TIMES-PL-PSE/Shared Documents/General/MODELE/2026/AGR_wyizolowany/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578EADD2-0B02-490A-91D6-A0F3802A5CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{578EADD2-0B02-490A-91D6-A0F3802A5CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA379C55-689C-4B10-A802-68E9DE82C29F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{008F860A-1793-4F78-8899-BE3F7B7A437A}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>Zbiory użytkownika: dobra | User Sets: Commodities</t>
   </si>
@@ -91,19 +91,16 @@
     <t>\I: tabele TFM_Csets i TFM_PSets nie akceptują wierszy komentarza?</t>
   </si>
   <si>
-    <t>OCGT</t>
-  </si>
-  <si>
-    <t>PPGAS</t>
-  </si>
-  <si>
     <t>GAS</t>
   </si>
   <si>
     <t>FOSS</t>
   </si>
   <si>
-    <t>ELE</t>
+    <t>AGR_NEW_BIOG_MAN,AGR_NEW_BIOG_MIX,AGR_NEW_BIOG_LIGN,AGR_NEW_BIO_CH4_MAN,AGR_NEW_BIO_CH4_MIX,AGR_NEW_BIO_CH4_LIGN</t>
+  </si>
+  <si>
+    <t>AGR_BIOG_BIO_CH4_PROC_SET</t>
   </si>
 </sst>
 </file>
@@ -506,6 +503,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -809,8 +810,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="65.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72.85546875" customWidth="1"/>
+    <col min="3" max="3" width="83.85546875" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -856,10 +858,10 @@
     <row r="7" spans="1:6" ht="15.75" thickBot="1">
       <c r="A7" s="7"/>
       <c r="B7" s="19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="1"/>
@@ -934,15 +936,13 @@
       <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="A15" s="3"/>
       <c r="B15" s="18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="1"/>
@@ -1004,8 +1004,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="d5167bf0dd55feede3e29f1a430471b5">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24bde18039da748f015df48b5e1e3648" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3a89f9027361f7d3c140af2fe110eadb">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff995f4215d3ca90fb464d6ddf93df71" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
     <xsd:import namespace="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
     <xsd:element name="properties">
@@ -1049,7 +1049,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Tagi obrazów" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b7b31e59-74a4-4436-bc03-9931855e0d9a" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b7b31e59-74a4-4436-bc03-9931855e0d9a" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -1120,7 +1120,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Udostępnianie" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1139,7 +1139,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Udostępnione dla — szczegóły" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -1156,8 +1156,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Typ zawartości"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Tytuł"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1247,15 +1247,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
@@ -1266,14 +1257,34 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4C2C1FE-7CE4-4DC1-BE6C-3DBF5388C19A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0893D5E0-3DCD-443E-A016-D13771A48900}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CCE832A-6182-4644-8024-858B12F38FDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C698EA37-445D-4B28-A644-33074FF3AABE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C698EA37-445D-4B28-A644-33074FF3AABE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CCE832A-6182-4644-8024-858B12F38FDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>